--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/8.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/8.xlsx
@@ -426,13 +426,13 @@
         <v>-9.751530320153647</v>
       </c>
       <c r="E2">
-        <v>-16.34777060202756</v>
+        <v>-27.13555119631397</v>
       </c>
       <c r="F2">
-        <v>-0.4321842723100938</v>
+        <v>-2.665064345536814</v>
       </c>
       <c r="G2">
-        <v>-9.349249907758846</v>
+        <v>-15.20082784951641</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.99220478194664</v>
       </c>
       <c r="E3">
-        <v>-16.26383080782137</v>
+        <v>-26.8253235559445</v>
       </c>
       <c r="F3">
-        <v>0.08973772186516549</v>
+        <v>-2.790446035624548</v>
       </c>
       <c r="G3">
-        <v>-8.864509898262142</v>
+        <v>-14.95591700106667</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.146803061558868</v>
       </c>
       <c r="E4">
-        <v>-17.4659912172156</v>
+        <v>-27.3322273509411</v>
       </c>
       <c r="F4">
-        <v>-0.4889721712416111</v>
+        <v>-2.784263101330052</v>
       </c>
       <c r="G4">
-        <v>-9.39929542467601</v>
+        <v>-14.9667904878904</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.279211529569572</v>
       </c>
       <c r="E5">
-        <v>-16.99546918239663</v>
+        <v>-28.20593301208498</v>
       </c>
       <c r="F5">
-        <v>0.07672572670199086</v>
+        <v>-2.751210413590949</v>
       </c>
       <c r="G5">
-        <v>-9.632837859743896</v>
+        <v>-14.96605554678068</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.403498707288936</v>
       </c>
       <c r="E6">
-        <v>-17.69414932314406</v>
+        <v>-27.84854131492563</v>
       </c>
       <c r="F6">
-        <v>-0.037117633832148</v>
+        <v>-2.908425434600864</v>
       </c>
       <c r="G6">
-        <v>-9.862169280885828</v>
+        <v>-14.76416854815931</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.550813385882244</v>
       </c>
       <c r="E7">
-        <v>-17.76817175927344</v>
+        <v>-29.05369957411294</v>
       </c>
       <c r="F7">
-        <v>0.4092829325972832</v>
+        <v>-2.943022199178785</v>
       </c>
       <c r="G7">
-        <v>-8.774492854503819</v>
+        <v>-14.72304826201602</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.734012841930651</v>
       </c>
       <c r="E8">
-        <v>-18.48550921293247</v>
+        <v>-28.42501605610207</v>
       </c>
       <c r="F8">
-        <v>0.1303194409283133</v>
+        <v>-2.522719347774553</v>
       </c>
       <c r="G8">
-        <v>-9.007532086649736</v>
+        <v>-14.23307262474896</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.966278263774152</v>
       </c>
       <c r="E9">
-        <v>-19.11657470827137</v>
+        <v>-29.6421159012476</v>
       </c>
       <c r="F9">
-        <v>0.06862098003300049</v>
+        <v>-2.636072314806234</v>
       </c>
       <c r="G9">
-        <v>-8.277983855615005</v>
+        <v>-13.97445446249386</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.260599921638378</v>
       </c>
       <c r="E10">
-        <v>-20.11590023838804</v>
+        <v>-29.33902513591422</v>
       </c>
       <c r="F10">
-        <v>0.3773568245259875</v>
+        <v>-2.619592773694941</v>
       </c>
       <c r="G10">
-        <v>-7.553447790526731</v>
+        <v>-13.85199407245068</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.61996640169822</v>
       </c>
       <c r="E11">
-        <v>-18.89640030201844</v>
+        <v>-30.35409164168155</v>
       </c>
       <c r="F11">
-        <v>0.3359947833694025</v>
+        <v>-2.617454757428316</v>
       </c>
       <c r="G11">
-        <v>-7.119544518331074</v>
+        <v>-13.47353416167397</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.039094913095808</v>
       </c>
       <c r="E12">
-        <v>-21.29214871951037</v>
+        <v>-30.80325286460634</v>
       </c>
       <c r="F12">
-        <v>0.6394497856695426</v>
+        <v>-2.604467613287225</v>
       </c>
       <c r="G12">
-        <v>-7.527360691677274</v>
+        <v>-13.43835630477368</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.505713997985339</v>
       </c>
       <c r="E13">
-        <v>-21.81311342630078</v>
+        <v>-30.70937306995333</v>
       </c>
       <c r="F13">
-        <v>0.168653799227666</v>
+        <v>-2.5700472909661</v>
       </c>
       <c r="G13">
-        <v>-6.780620797657108</v>
+        <v>-13.15159022907093</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.01545065501892</v>
       </c>
       <c r="E14">
-        <v>-21.8355565434828</v>
+        <v>-31.18498963803093</v>
       </c>
       <c r="F14">
-        <v>0.2249198266954196</v>
+        <v>-2.6319785231016</v>
       </c>
       <c r="G14">
-        <v>-5.94622096830258</v>
+        <v>-12.73869236832195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.5557517739181348</v>
       </c>
       <c r="E15">
-        <v>-23.42644116169545</v>
+        <v>-32.61013890027385</v>
       </c>
       <c r="F15">
-        <v>0.713577899443862</v>
+        <v>-2.157087916587685</v>
       </c>
       <c r="G15">
-        <v>-5.629368654738935</v>
+        <v>-12.17688285867101</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.1171895845662707</v>
       </c>
       <c r="E16">
-        <v>-25.31209321001538</v>
+        <v>-32.67095404195987</v>
       </c>
       <c r="F16">
-        <v>1.113763848471109</v>
+        <v>-2.3066687036134</v>
       </c>
       <c r="G16">
-        <v>-5.190873655880309</v>
+        <v>-11.85382327222123</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.3085319435401828</v>
       </c>
       <c r="E17">
-        <v>-24.41404700108026</v>
+        <v>-33.57761114422056</v>
       </c>
       <c r="F17">
-        <v>1.016309737001358</v>
+        <v>-2.329199468602144</v>
       </c>
       <c r="G17">
-        <v>-4.033182501888254</v>
+        <v>-11.9597011396582</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.722054317187897</v>
       </c>
       <c r="E18">
-        <v>-25.57838559556243</v>
+        <v>-34.27701131233521</v>
       </c>
       <c r="F18">
-        <v>1.202954166730531</v>
+        <v>-2.255145907894076</v>
       </c>
       <c r="G18">
-        <v>-3.940894423889991</v>
+        <v>-11.12534434739568</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.125890009242104</v>
       </c>
       <c r="E19">
-        <v>-26.50789564190284</v>
+        <v>-34.8586485138804</v>
       </c>
       <c r="F19">
-        <v>1.275545658972658</v>
+        <v>-1.983718902855776</v>
       </c>
       <c r="G19">
-        <v>-3.025826531380042</v>
+        <v>-11.51603837921277</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.518040608046884</v>
       </c>
       <c r="E20">
-        <v>-28.31832520848135</v>
+        <v>-35.90714874324635</v>
       </c>
       <c r="F20">
-        <v>1.184430214869129</v>
+        <v>-1.980102250775154</v>
       </c>
       <c r="G20">
-        <v>-3.177558765081458</v>
+        <v>-11.32585415907272</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.897402141525275</v>
       </c>
       <c r="E21">
-        <v>-27.59558528533117</v>
+        <v>-35.94991112330078</v>
       </c>
       <c r="F21">
-        <v>1.136760984307629</v>
+        <v>-1.911632714729358</v>
       </c>
       <c r="G21">
-        <v>-3.623548839040994</v>
+        <v>-11.01510318093795</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.260898404812526</v>
       </c>
       <c r="E22">
-        <v>-29.85792938703115</v>
+        <v>-36.50798441034705</v>
       </c>
       <c r="F22">
-        <v>1.588772911523624</v>
+        <v>-1.528188070912689</v>
       </c>
       <c r="G22">
-        <v>-2.191135374018058</v>
+        <v>-10.87456059115927</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.606245383291157</v>
       </c>
       <c r="E23">
-        <v>-29.0215021239184</v>
+        <v>-37.53736995092663</v>
       </c>
       <c r="F23">
-        <v>1.459542626482484</v>
+        <v>-1.6799574046166</v>
       </c>
       <c r="G23">
-        <v>-2.13966301197347</v>
+        <v>-10.69415903308777</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.928608611194466</v>
       </c>
       <c r="E24">
-        <v>-29.63399861158885</v>
+        <v>-37.2344829669236</v>
       </c>
       <c r="F24">
-        <v>1.657578764734956</v>
+        <v>-1.176935441103615</v>
       </c>
       <c r="G24">
-        <v>-1.815292449490139</v>
+        <v>-10.5634388319241</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.227233866711144</v>
       </c>
       <c r="E25">
-        <v>-29.07104815803632</v>
+        <v>-37.59631256861046</v>
       </c>
       <c r="F25">
-        <v>1.490700837971385</v>
+        <v>-1.241617681383811</v>
       </c>
       <c r="G25">
-        <v>-1.223188137609331</v>
+        <v>-11.14166533690429</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.499954498153561</v>
       </c>
       <c r="E26">
-        <v>-31.041568337734</v>
+        <v>-37.7653605033168</v>
       </c>
       <c r="F26">
-        <v>1.607253788280081</v>
+        <v>-1.199701462434753</v>
       </c>
       <c r="G26">
-        <v>-1.385375074123765</v>
+        <v>-11.01819854101717</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.74355975928602</v>
       </c>
       <c r="E27">
-        <v>-30.78283850377976</v>
+        <v>-37.87348234872394</v>
       </c>
       <c r="F27">
-        <v>1.869080843487337</v>
+        <v>-1.271591327486708</v>
       </c>
       <c r="G27">
-        <v>-1.469817159193956</v>
+        <v>-11.04965203418578</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.950491533850463</v>
       </c>
       <c r="E28">
-        <v>-30.03577161826038</v>
+        <v>-37.70069842296127</v>
       </c>
       <c r="F28">
-        <v>1.652393184793431</v>
+        <v>-1.079861550271749</v>
       </c>
       <c r="G28">
-        <v>-1.412329535904511</v>
+        <v>-11.16052551484152</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.114914121241412</v>
       </c>
       <c r="E29">
-        <v>-29.88581572997038</v>
+        <v>-37.91370878333407</v>
       </c>
       <c r="F29">
-        <v>1.561012663121007</v>
+        <v>-1.17539550610181</v>
       </c>
       <c r="G29">
-        <v>-1.43241461569127</v>
+        <v>-11.00728367237419</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.228017094857731</v>
       </c>
       <c r="E30">
-        <v>-29.46543748783834</v>
+        <v>-37.50339054621008</v>
       </c>
       <c r="F30">
-        <v>1.651271575330041</v>
+        <v>-1.117534871383668</v>
       </c>
       <c r="G30">
-        <v>-1.491286047016129</v>
+        <v>-10.84759619774191</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.279097883607248</v>
       </c>
       <c r="E31">
-        <v>-29.3705976566957</v>
+        <v>-37.47472756997853</v>
       </c>
       <c r="F31">
-        <v>1.568507731381537</v>
+        <v>-1.065695639316474</v>
       </c>
       <c r="G31">
-        <v>-1.784126973783441</v>
+        <v>-11.26637027682309</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.256277553528813</v>
       </c>
       <c r="E32">
-        <v>-28.2492795652864</v>
+        <v>-37.04865250754484</v>
       </c>
       <c r="F32">
-        <v>1.85068280347116</v>
+        <v>-1.194463695346852</v>
       </c>
       <c r="G32">
-        <v>-2.294222451565424</v>
+        <v>-11.33359421454354</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.14969730375344</v>
       </c>
       <c r="E33">
-        <v>-29.27807187577098</v>
+        <v>-36.8411691496984</v>
       </c>
       <c r="F33">
-        <v>1.314795363252104</v>
+        <v>-1.158138956366691</v>
       </c>
       <c r="G33">
-        <v>-2.514145302284748</v>
+        <v>-11.13237925666663</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.950478765979744</v>
       </c>
       <c r="E34">
-        <v>-29.23288676212244</v>
+        <v>-36.58691571230074</v>
       </c>
       <c r="F34">
-        <v>1.992323688941042</v>
+        <v>-0.9317602274274337</v>
       </c>
       <c r="G34">
-        <v>-2.082903708702665</v>
+        <v>-11.76843768167235</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.65196394318128</v>
       </c>
       <c r="E35">
-        <v>-28.44630441241213</v>
+        <v>-36.25428571101533</v>
       </c>
       <c r="F35">
-        <v>1.928552652803925</v>
+        <v>-1.167251826164888</v>
       </c>
       <c r="G35">
-        <v>-3.380472032820007</v>
+        <v>-12.24129283268307</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.252093997877001</v>
       </c>
       <c r="E36">
-        <v>-29.19126102904394</v>
+        <v>-35.51211410589824</v>
       </c>
       <c r="F36">
-        <v>1.912795448067873</v>
+        <v>-1.220886958761351</v>
       </c>
       <c r="G36">
-        <v>-3.1403018855825</v>
+        <v>-11.81230903115877</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.750975306677813</v>
       </c>
       <c r="E37">
-        <v>-26.24622229984361</v>
+        <v>-35.29975358154554</v>
       </c>
       <c r="F37">
-        <v>2.199745229867232</v>
+        <v>-0.8245272387676349</v>
       </c>
       <c r="G37">
-        <v>-3.702253748691627</v>
+        <v>-11.64871511279014</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.151530143650721</v>
       </c>
       <c r="E38">
-        <v>-27.09441906690229</v>
+        <v>-34.6481174930268</v>
       </c>
       <c r="F38">
-        <v>2.32637112779397</v>
+        <v>-1.183752904828654</v>
       </c>
       <c r="G38">
-        <v>-3.621436710986939</v>
+        <v>-12.09945913014407</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.460460057487723</v>
       </c>
       <c r="E39">
-        <v>-25.8145817428545</v>
+        <v>-34.00102119970074</v>
       </c>
       <c r="F39">
-        <v>2.380359144904026</v>
+        <v>-0.9576467087649182</v>
       </c>
       <c r="G39">
-        <v>-3.686359819557586</v>
+        <v>-12.19648459880903</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6877519229521055</v>
       </c>
       <c r="E40">
-        <v>-26.78631980931643</v>
+        <v>-33.74626963016224</v>
       </c>
       <c r="F40">
-        <v>2.150546833080164</v>
+        <v>-0.8944339922572879</v>
       </c>
       <c r="G40">
-        <v>-3.506468085499129</v>
+        <v>-11.80755508776437</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.155233561551233</v>
       </c>
       <c r="E41">
-        <v>-26.2929742654988</v>
+        <v>-33.58732698520402</v>
       </c>
       <c r="F41">
-        <v>2.704706401470172</v>
+        <v>-0.7712342219085286</v>
       </c>
       <c r="G41">
-        <v>-4.131022364755874</v>
+        <v>-11.90274982474612</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.05441446622906</v>
       </c>
       <c r="E42">
-        <v>-23.98018296335338</v>
+        <v>-32.80893664497358</v>
       </c>
       <c r="F42">
-        <v>2.871272862090291</v>
+        <v>-0.7726407897584823</v>
       </c>
       <c r="G42">
-        <v>-3.888693741826763</v>
+        <v>-11.98806258329314</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.991154726865438</v>
       </c>
       <c r="E43">
-        <v>-23.74915380490406</v>
+        <v>-31.89937905511097</v>
       </c>
       <c r="F43">
-        <v>2.843055354881329</v>
+        <v>-0.6569841329796152</v>
       </c>
       <c r="G43">
-        <v>-3.809333344159354</v>
+        <v>-12.5268770436283</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.947123988854953</v>
       </c>
       <c r="E44">
-        <v>-23.07900305040496</v>
+        <v>-31.76179948628393</v>
       </c>
       <c r="F44">
-        <v>2.447624234746151</v>
+        <v>-0.566857759555029</v>
       </c>
       <c r="G44">
-        <v>-5.164362807201825</v>
+        <v>-12.1049579462848</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.904382836698328</v>
       </c>
       <c r="E45">
-        <v>-23.87934290415058</v>
+        <v>-31.31810865996041</v>
       </c>
       <c r="F45">
-        <v>2.681682757876763</v>
+        <v>-0.5400004316214635</v>
       </c>
       <c r="G45">
-        <v>-4.361684625204594</v>
+        <v>-12.20069561273498</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.846059175579411</v>
       </c>
       <c r="E46">
-        <v>-22.55999464438586</v>
+        <v>-30.90301967546933</v>
       </c>
       <c r="F46">
-        <v>2.663001416208828</v>
+        <v>-0.5211061995310096</v>
       </c>
       <c r="G46">
-        <v>-5.612508046307426</v>
+        <v>-12.10834132382594</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.750443274249086</v>
       </c>
       <c r="E47">
-        <v>-21.02538990114054</v>
+        <v>-30.25161227488797</v>
       </c>
       <c r="F47">
-        <v>2.885635096120029</v>
+        <v>-0.8625368770450902</v>
       </c>
       <c r="G47">
-        <v>-4.876636673292688</v>
+        <v>-12.49968091202318</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.601559072773344</v>
       </c>
       <c r="E48">
-        <v>-20.86932510141419</v>
+        <v>-29.61665908461348</v>
       </c>
       <c r="F48">
-        <v>3.019698076589101</v>
+        <v>-0.5865331421063229</v>
       </c>
       <c r="G48">
-        <v>-4.335329372166457</v>
+        <v>-12.31825639538004</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.386664252482471</v>
       </c>
       <c r="E49">
-        <v>-19.33165458126567</v>
+        <v>-29.06544643568883</v>
       </c>
       <c r="F49">
-        <v>2.845378097078779</v>
+        <v>-0.5438937584146212</v>
       </c>
       <c r="G49">
-        <v>-4.827521419672061</v>
+        <v>-12.03295358080565</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.095965097661978</v>
       </c>
       <c r="E50">
-        <v>-18.71350429379665</v>
+        <v>-29.17798354325345</v>
       </c>
       <c r="F50">
-        <v>3.22075444239218</v>
+        <v>-0.476081946086648</v>
       </c>
       <c r="G50">
-        <v>-5.144300901233842</v>
+        <v>-12.1868045636522</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.716570286360604</v>
       </c>
       <c r="E51">
-        <v>-19.50429359586009</v>
+        <v>-28.14886065416631</v>
       </c>
       <c r="F51">
-        <v>3.169973863865765</v>
+        <v>-0.5531350251602525</v>
       </c>
       <c r="G51">
-        <v>-4.758374054993303</v>
+        <v>-12.43303963031765</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.244235994509769</v>
       </c>
       <c r="E52">
-        <v>-18.41465670860846</v>
+        <v>-28.47090308322179</v>
       </c>
       <c r="F52">
-        <v>3.057471630156758</v>
+        <v>-0.4949488420528095</v>
       </c>
       <c r="G52">
-        <v>-5.360088880574616</v>
+        <v>-12.7432741633483</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.68019763509367</v>
       </c>
       <c r="E53">
-        <v>-18.04953943479202</v>
+        <v>-27.50710796016931</v>
       </c>
       <c r="F53">
-        <v>3.273733508005625</v>
+        <v>-0.3712272002402866</v>
       </c>
       <c r="G53">
-        <v>-5.1237788294359</v>
+        <v>-12.58589413895688</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.02632391584109</v>
       </c>
       <c r="E54">
-        <v>-17.61605578888178</v>
+        <v>-26.82011128236167</v>
       </c>
       <c r="F54">
-        <v>3.479412163916326</v>
+        <v>-0.3294161839513843</v>
       </c>
       <c r="G54">
-        <v>-5.889974799590362</v>
+        <v>-12.47845700457091</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.27926272093164</v>
       </c>
       <c r="E55">
-        <v>-16.29483274087789</v>
+        <v>-26.32238217570461</v>
       </c>
       <c r="F55">
-        <v>3.257035277899993</v>
+        <v>-0.3727033509520753</v>
       </c>
       <c r="G55">
-        <v>-5.217914191845076</v>
+        <v>-12.75531792802017</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.44542039932262</v>
       </c>
       <c r="E56">
-        <v>-15.50363587615375</v>
+        <v>-26.60742697211742</v>
       </c>
       <c r="F56">
-        <v>3.070964078413557</v>
+        <v>-0.1679715189827747</v>
       </c>
       <c r="G56">
-        <v>-5.30602105082724</v>
+        <v>-12.76005531868686</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.53434774409751</v>
       </c>
       <c r="E57">
-        <v>-15.88903165657654</v>
+        <v>-25.61859844475054</v>
       </c>
       <c r="F57">
-        <v>3.115972592877265</v>
+        <v>-0.516625560249267</v>
       </c>
       <c r="G57">
-        <v>-5.475921558448176</v>
+        <v>-12.6475861550812</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.55163600361263</v>
       </c>
       <c r="E58">
-        <v>-14.2961454528525</v>
+        <v>-25.33516125661045</v>
       </c>
       <c r="F58">
-        <v>3.239863221639959</v>
+        <v>-0.4597921011105958</v>
       </c>
       <c r="G58">
-        <v>-6.202053306486379</v>
+        <v>-12.86033836416246</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.49519107317065</v>
       </c>
       <c r="E59">
-        <v>-13.64735098177357</v>
+        <v>-24.90309049459061</v>
       </c>
       <c r="F59">
-        <v>3.100553362041555</v>
+        <v>-0.4273805697412595</v>
       </c>
       <c r="G59">
-        <v>-5.810601159740797</v>
+        <v>-12.85818650956194</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.3735918992395</v>
       </c>
       <c r="E60">
-        <v>-15.06215494514597</v>
+        <v>-24.95891299368316</v>
       </c>
       <c r="F60">
-        <v>3.077241446591971</v>
+        <v>-0.3791530195502723</v>
       </c>
       <c r="G60">
-        <v>-6.316505486870063</v>
+        <v>-12.8541708178228</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.19464049548596</v>
       </c>
       <c r="E61">
-        <v>-14.23547295809773</v>
+        <v>-25.07899453894456</v>
       </c>
       <c r="F61">
-        <v>3.047305905389603</v>
+        <v>-0.3647162324542825</v>
       </c>
       <c r="G61">
-        <v>-5.917915803941812</v>
+        <v>-12.9685733400234</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.960638333485052</v>
       </c>
       <c r="E62">
-        <v>-12.4448101805627</v>
+        <v>-24.37024307200407</v>
       </c>
       <c r="F62">
-        <v>2.952124834073134</v>
+        <v>-0.6049941380451127</v>
       </c>
       <c r="G62">
-        <v>-5.549372632327985</v>
+        <v>-12.74044364691222</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.666726592613363</v>
       </c>
       <c r="E63">
-        <v>-13.08310312041784</v>
+        <v>-24.38799016164013</v>
       </c>
       <c r="F63">
-        <v>2.512139144810982</v>
+        <v>-0.5490809950909517</v>
       </c>
       <c r="G63">
-        <v>-5.999894843130784</v>
+        <v>-12.7714138004321</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.319784259664454</v>
       </c>
       <c r="E64">
-        <v>-13.00723306689333</v>
+        <v>-24.12076038197349</v>
       </c>
       <c r="F64">
-        <v>2.440354482419183</v>
+        <v>-0.6219209975539178</v>
       </c>
       <c r="G64">
-        <v>-5.798014465600487</v>
+        <v>-12.71667392994025</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.92533213267448</v>
       </c>
       <c r="E65">
-        <v>-11.8318721666765</v>
+        <v>-24.6278453159304</v>
       </c>
       <c r="F65">
-        <v>2.185828657500201</v>
+        <v>-0.5812050829715165</v>
       </c>
       <c r="G65">
-        <v>-5.582663478270897</v>
+        <v>-12.85828582592812</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.484360237761098</v>
       </c>
       <c r="E66">
-        <v>-13.02983468066561</v>
+        <v>-23.7316376674424</v>
       </c>
       <c r="F66">
-        <v>1.826080291608015</v>
+        <v>-0.850489929906177</v>
       </c>
       <c r="G66">
-        <v>-4.812124072368911</v>
+        <v>-13.01009751272248</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.993876515716239</v>
       </c>
       <c r="E67">
-        <v>-12.22685925504753</v>
+        <v>-23.93589448755836</v>
       </c>
       <c r="F67">
-        <v>2.203625302781945</v>
+        <v>-0.9186960451178826</v>
       </c>
       <c r="G67">
-        <v>-5.580799641132288</v>
+        <v>-13.01265325387879</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.462046041694681</v>
       </c>
       <c r="E68">
-        <v>-11.34698128383119</v>
+        <v>-24.3186637530567</v>
       </c>
       <c r="F68">
-        <v>2.06841917529701</v>
+        <v>-1.140044927187341</v>
       </c>
       <c r="G68">
-        <v>-5.678318381082598</v>
+        <v>-12.48246276467343</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.89470199181923</v>
       </c>
       <c r="E69">
-        <v>-11.50029729983487</v>
+        <v>-23.96503068932372</v>
       </c>
       <c r="F69">
-        <v>1.75884502299239</v>
+        <v>-1.092539713371595</v>
       </c>
       <c r="G69">
-        <v>-5.546714264259951</v>
+        <v>-13.01750320309383</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.294203832089617</v>
       </c>
       <c r="E70">
-        <v>-12.62152935023802</v>
+        <v>-23.86734697650426</v>
       </c>
       <c r="F70">
-        <v>1.685405282529797</v>
+        <v>-1.191064075525763</v>
       </c>
       <c r="G70">
-        <v>-4.570550253822753</v>
+        <v>-12.28058900823422</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.660571366297432</v>
       </c>
       <c r="E71">
-        <v>-11.25098669181659</v>
+        <v>-23.80785188499149</v>
       </c>
       <c r="F71">
-        <v>1.400680495574357</v>
+        <v>-1.335630754662333</v>
       </c>
       <c r="G71">
-        <v>-4.939123220346431</v>
+        <v>-12.33790117261008</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.003352119116059</v>
       </c>
       <c r="E72">
-        <v>-11.30059612457062</v>
+        <v>-24.00170680031184</v>
       </c>
       <c r="F72">
-        <v>1.183651549510497</v>
+        <v>-1.258016870857033</v>
       </c>
       <c r="G72">
-        <v>-5.144698166698555</v>
+        <v>-12.27325946041027</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.328007280512864</v>
       </c>
       <c r="E73">
-        <v>-11.45650242770669</v>
+        <v>-23.52324635055742</v>
       </c>
       <c r="F73">
-        <v>1.163310159567353</v>
+        <v>-1.522159212955114</v>
       </c>
       <c r="G73">
-        <v>-4.418612766297901</v>
+        <v>-12.62946422879923</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.637928281584694</v>
       </c>
       <c r="E74">
-        <v>-11.08475999641703</v>
+        <v>-23.61454944350007</v>
       </c>
       <c r="F74">
-        <v>0.8377203518970071</v>
+        <v>-1.513549162170416</v>
       </c>
       <c r="G74">
-        <v>-4.438280717346712</v>
+        <v>-12.35826433822214</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.933357625851089</v>
       </c>
       <c r="E75">
-        <v>-12.56907603580718</v>
+        <v>-24.37953550066781</v>
       </c>
       <c r="F75">
-        <v>0.9141604390925399</v>
+        <v>-1.558854232164327</v>
       </c>
       <c r="G75">
-        <v>-3.888852648012648</v>
+        <v>-11.93241893386907</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.220887976648841</v>
       </c>
       <c r="E76">
-        <v>-11.73962262266624</v>
+        <v>-23.92103203586519</v>
       </c>
       <c r="F76">
-        <v>0.9208453640331319</v>
+        <v>-1.825624984031491</v>
       </c>
       <c r="G76">
-        <v>-4.195170805670332</v>
+        <v>-11.72299051250923</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.501135836733893</v>
       </c>
       <c r="E77">
-        <v>-11.91996457154771</v>
+        <v>-23.92793343025288</v>
       </c>
       <c r="F77">
-        <v>0.9314186455624648</v>
+        <v>-1.946119306442707</v>
       </c>
       <c r="G77">
-        <v>-3.430865157018793</v>
+        <v>-11.94884255028939</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.7753410798429192</v>
       </c>
       <c r="E78">
-        <v>-12.12898081784574</v>
+        <v>-24.24286615511632</v>
       </c>
       <c r="F78">
-        <v>0.3251075505944086</v>
+        <v>-1.820807199216809</v>
       </c>
       <c r="G78">
-        <v>-3.791151828057676</v>
+        <v>-11.57428411743071</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.04156555204315016</v>
       </c>
       <c r="E79">
-        <v>-13.04097925519849</v>
+        <v>-24.93377996294059</v>
       </c>
       <c r="F79">
-        <v>0.7547361622193582</v>
+        <v>-2.146638061801369</v>
       </c>
       <c r="G79">
-        <v>-2.559486533990606</v>
+        <v>-11.9828418529777</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.6961396509266224</v>
       </c>
       <c r="E80">
-        <v>-13.24417188392266</v>
+        <v>-24.68360441638684</v>
       </c>
       <c r="F80">
-        <v>0.6416557280631977</v>
+        <v>-2.036603534585302</v>
       </c>
       <c r="G80">
-        <v>-2.440906103319451</v>
+        <v>-11.3720991697108</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.437555247663999</v>
       </c>
       <c r="E81">
-        <v>-13.77211044068489</v>
+        <v>-25.38152830197499</v>
       </c>
       <c r="F81">
-        <v>0.6546478424087051</v>
+        <v>-2.039497850290684</v>
       </c>
       <c r="G81">
-        <v>-2.383249642207504</v>
+        <v>-11.24439487553341</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.176923449223432</v>
       </c>
       <c r="E82">
-        <v>-13.97415283701111</v>
+        <v>-25.40770288173932</v>
       </c>
       <c r="F82">
-        <v>0.4384091588471166</v>
+        <v>-2.274970396577874</v>
       </c>
       <c r="G82">
-        <v>-3.018457257009624</v>
+        <v>-11.67853319646236</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.910760324066063</v>
       </c>
       <c r="E83">
-        <v>-15.17273575193927</v>
+        <v>-26.19776309948753</v>
       </c>
       <c r="F83">
-        <v>0.1322097753415017</v>
+        <v>-2.252886949986642</v>
       </c>
       <c r="G83">
-        <v>-1.751481684220688</v>
+        <v>-11.47261064282861</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.632361889460703</v>
       </c>
       <c r="E84">
-        <v>-16.73120102473101</v>
+        <v>-26.85494430442867</v>
       </c>
       <c r="F84">
-        <v>0.2058002786714042</v>
+        <v>-2.15757168315092</v>
       </c>
       <c r="G84">
-        <v>-1.332131570215667</v>
+        <v>-11.30255785011287</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>4.337233992442308</v>
       </c>
       <c r="E85">
-        <v>-16.77524949140362</v>
+        <v>-27.36863175348876</v>
       </c>
       <c r="F85">
-        <v>0.1248563579068505</v>
+        <v>-2.351911646052101</v>
       </c>
       <c r="G85">
-        <v>-1.492686407779241</v>
+        <v>-11.47403748795604</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.015129976694118</v>
       </c>
       <c r="E86">
-        <v>-19.02435233510516</v>
+        <v>-28.35707083209098</v>
       </c>
       <c r="F86">
-        <v>0.01736491861737828</v>
+        <v>-2.473030557485028</v>
       </c>
       <c r="G86">
-        <v>-1.728264828353778</v>
+        <v>-11.36570650627447</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.661394119311091</v>
       </c>
       <c r="E87">
-        <v>-19.50270862995741</v>
+        <v>-29.23639180100438</v>
       </c>
       <c r="F87">
-        <v>-0.00543175230766411</v>
+        <v>-2.47646662547184</v>
       </c>
       <c r="G87">
-        <v>-1.019460475668121</v>
+        <v>-11.20023550858508</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>6.270968309588045</v>
       </c>
       <c r="E88">
-        <v>-20.31897965526201</v>
+        <v>-29.59453975332302</v>
       </c>
       <c r="F88">
-        <v>0.1033362011495222</v>
+        <v>-2.520955753573993</v>
       </c>
       <c r="G88">
-        <v>-1.717952478998949</v>
+        <v>-11.18306039832733</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>6.838755410347106</v>
       </c>
       <c r="E89">
-        <v>-20.40638373208406</v>
+        <v>-30.75040104446282</v>
       </c>
       <c r="F89">
-        <v>-0.09874154166120883</v>
+        <v>-2.62648976069065</v>
       </c>
       <c r="G89">
-        <v>-0.9580001977315514</v>
+        <v>-11.26563864625892</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>7.352420524261311</v>
       </c>
       <c r="E90">
-        <v>-23.91174413567546</v>
+        <v>-31.85973452941082</v>
       </c>
       <c r="F90">
-        <v>0.2256694991949532</v>
+        <v>-2.649643457966299</v>
       </c>
       <c r="G90">
-        <v>-0.7701466016511472</v>
+        <v>-11.41235540346834</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>7.80639298184954</v>
       </c>
       <c r="E91">
-        <v>-24.73611660097979</v>
+        <v>-33.07277006913446</v>
       </c>
       <c r="F91">
-        <v>0.0516841801153618</v>
+        <v>-2.486778971269291</v>
       </c>
       <c r="G91">
-        <v>-1.273144269796933</v>
+        <v>-11.13690477241882</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>8.193548834381003</v>
       </c>
       <c r="E92">
-        <v>-26.50091273498301</v>
+        <v>-34.74764429476738</v>
       </c>
       <c r="F92">
-        <v>-0.4120889074855806</v>
+        <v>-2.993714142393102</v>
       </c>
       <c r="G92">
-        <v>-1.205963369168503</v>
+        <v>-11.72873099847433</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>8.504951667410976</v>
       </c>
       <c r="E93">
-        <v>-27.66712611770435</v>
+        <v>-35.11846971007048</v>
       </c>
       <c r="F93">
-        <v>-0.02898058083444846</v>
+        <v>-2.945311806680123</v>
       </c>
       <c r="G93">
-        <v>-2.071250588404431</v>
+        <v>-11.7213948295593</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>8.725036378663299</v>
       </c>
       <c r="E94">
-        <v>-30.64601292587501</v>
+        <v>-36.3807297622575</v>
       </c>
       <c r="F94">
-        <v>-0.07102519673094017</v>
+        <v>-3.134490212294461</v>
       </c>
       <c r="G94">
-        <v>-2.072137814608956</v>
+        <v>-11.69546663689573</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.852261561661363</v>
       </c>
       <c r="E95">
-        <v>-32.22276644094672</v>
+        <v>-38.14901961395765</v>
       </c>
       <c r="F95">
-        <v>-0.4527070747144515</v>
+        <v>-3.127023308525626</v>
       </c>
       <c r="G95">
-        <v>-2.408075423206499</v>
+        <v>-11.69751917513008</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.878725110535861</v>
       </c>
       <c r="E96">
-        <v>-33.84733384882842</v>
+        <v>-39.97325423354854</v>
       </c>
       <c r="F96">
-        <v>-0.5482824489146529</v>
+        <v>-3.403366674099541</v>
       </c>
       <c r="G96">
-        <v>-2.531783888917985</v>
+        <v>-11.94741570516196</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>8.809738795661413</v>
       </c>
       <c r="E97">
-        <v>-35.68189112491981</v>
+        <v>-41.60145800605841</v>
       </c>
       <c r="F97">
-        <v>-0.4988512808873981</v>
+        <v>-3.605649023658763</v>
       </c>
       <c r="G97">
-        <v>-2.3101362439727</v>
+        <v>-12.44233233164639</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>8.622394770636939</v>
       </c>
       <c r="E98">
-        <v>-37.92087962192522</v>
+        <v>-42.84222592060502</v>
       </c>
       <c r="F98">
-        <v>-0.9588014529244208</v>
+        <v>-3.544215640332347</v>
       </c>
       <c r="G98">
-        <v>-3.41252473473123</v>
+        <v>-12.29777736067411</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>8.347124870171038</v>
       </c>
       <c r="E99">
-        <v>-40.24249691991159</v>
+        <v>-44.42529892115444</v>
       </c>
       <c r="F99">
-        <v>-0.9865708133684685</v>
+        <v>-3.744360801992346</v>
       </c>
       <c r="G99">
-        <v>-2.613147166636653</v>
+        <v>-12.62981845717193</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>7.953726997072433</v>
       </c>
       <c r="E100">
-        <v>-42.32999664017541</v>
+        <v>-46.21132680554263</v>
       </c>
       <c r="F100">
-        <v>-0.8277951481716789</v>
+        <v>-3.855660246232488</v>
       </c>
       <c r="G100">
-        <v>-2.9337172228409</v>
+        <v>-13.17411187037459</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.505352230896524</v>
       </c>
       <c r="E101">
-        <v>-45.2205804694335</v>
+        <v>-48.41458337839052</v>
       </c>
       <c r="F101">
-        <v>-0.7673392383805654</v>
+        <v>-4.122560223414489</v>
       </c>
       <c r="G101">
-        <v>-3.696261661265546</v>
+        <v>-13.44480524748418</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.900484286313219</v>
       </c>
       <c r="E102">
-        <v>-46.76198924487534</v>
+        <v>-50.31736437964447</v>
       </c>
       <c r="F102">
-        <v>-0.7583961838999419</v>
+        <v>-4.34046558219051</v>
       </c>
       <c r="G102">
-        <v>-4.34993880963126</v>
+        <v>-13.47283232601965</v>
       </c>
     </row>
   </sheetData>
